--- a/data.mn/public/datasets/mongolbank-lending-rate-mnt-monthly.xlsx
+++ b/data.mn/public/datasets/mongolbank-lending-rate-mnt-monthly.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B126"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1681,6 +1681,26 @@
       </c>
       <c r="B126" t="n">
         <v>16.9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>17.04</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>17.09</v>
       </c>
     </row>
   </sheetData>
@@ -1694,7 +1714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B126"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2963,6 +2983,26 @@
         <v>16.9</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>17.04</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>17.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
